--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.9569369087795</v>
+        <v>8.443002247676668</v>
       </c>
       <c r="D2" t="n">
-        <v>52.33124396318417</v>
+        <v>8.503827144017428</v>
       </c>
       <c r="E2" t="n">
-        <v>12.08496029153249</v>
+        <v>1.963806047374031</v>
       </c>
       <c r="F2" t="n">
-        <v>11.5905478444526</v>
+        <v>1.883464024723548</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.07353782693704</v>
+        <v>10.73694989687727</v>
       </c>
       <c r="D3" t="n">
-        <v>65.50464877473173</v>
+        <v>10.64450542589391</v>
       </c>
       <c r="E3" t="n">
-        <v>12.08496029153249</v>
+        <v>1.963806047374031</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5905478444526</v>
+        <v>1.883464024723548</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.48194250217712</v>
+        <v>5.928315656603782</v>
       </c>
       <c r="D4" t="n">
-        <v>37.13768807712924</v>
+        <v>6.034874312533502</v>
       </c>
       <c r="E4" t="n">
-        <v>12.08496029153249</v>
+        <v>1.963806047374031</v>
       </c>
       <c r="F4" t="n">
-        <v>11.5905478444526</v>
+        <v>1.883464024723548</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
